--- a/resources/templates/standard/M1100-03.xlsx
+++ b/resources/templates/standard/M1100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>설비 비가동 시간 이력관리 대장</t>
   </si>
@@ -807,12 +810,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -853,16 +858,16 @@
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
       <c r="AR1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS1" s="3"/>
       <c r="AT1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
       <c r="AW1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX1" s="4"/>
       <c r="AY1" s="4"/>
@@ -975,7 +980,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -989,7 +994,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
@@ -1003,7 +1008,7 @@
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z4" s="8"/>
       <c r="AA4" s="8"/>
@@ -1017,7 +1022,7 @@
       <c r="AI4" s="7"/>
       <c r="AJ4" s="7"/>
       <c r="AK4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL4" s="8"/>
       <c r="AM4" s="8"/>
@@ -1036,7 +1041,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1062,7 +1067,7 @@
       <c r="W5" s="10"/>
       <c r="X5" s="10"/>
       <c r="Y5" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11"/>
@@ -1093,14 +1098,14 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -1121,14 +1126,14 @@
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE6" s="13"/>
       <c r="AF6" s="13"/>
@@ -1159,7 +1164,7 @@
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -1173,7 +1178,7 @@
       <c r="P7" s="14"/>
       <c r="Q7" s="14"/>
       <c r="R7" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
@@ -1187,7 +1192,7 @@
       <c r="AB7" s="12"/>
       <c r="AC7" s="12"/>
       <c r="AD7" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE7" s="14"/>
       <c r="AF7" s="14"/>
@@ -1218,7 +1223,7 @@
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -1244,7 +1249,7 @@
       <c r="AB8" s="15"/>
       <c r="AC8" s="15"/>
       <c r="AD8" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE8" s="18"/>
       <c r="AF8" s="18"/>
@@ -1275,7 +1280,7 @@
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -1301,7 +1306,7 @@
       <c r="AB9" s="15"/>
       <c r="AC9" s="15"/>
       <c r="AD9" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
@@ -1332,7 +1337,7 @@
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
       <c r="F10" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
@@ -1358,7 +1363,7 @@
       <c r="AB10" s="15"/>
       <c r="AC10" s="15"/>
       <c r="AD10" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE10" s="18"/>
       <c r="AF10" s="18"/>
@@ -1384,7 +1389,7 @@
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -1410,7 +1415,7 @@
       <c r="W11" s="20"/>
       <c r="X11" s="20"/>
       <c r="Y11" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z11" s="21"/>
       <c r="AA11" s="21"/>
@@ -1441,14 +1446,14 @@
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" s="23"/>
       <c r="H12" s="23"/>
@@ -1710,7 +1715,7 @@
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
@@ -1736,7 +1741,7 @@
       <c r="W17" s="24"/>
       <c r="X17" s="24"/>
       <c r="Y17" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -2085,14 +2090,14 @@
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="24"/>
       <c r="C24" s="24"/>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
@@ -2110,7 +2115,7 @@
       <c r="T24" s="24"/>
       <c r="U24" s="24"/>
       <c r="V24" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
@@ -2128,7 +2133,7 @@
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AM24" s="4"/>
       <c r="AN24" s="4"/>
@@ -2151,7 +2156,7 @@
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
       <c r="F25" s="26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
@@ -2169,31 +2174,31 @@
       <c r="T25" s="26"/>
       <c r="U25" s="26"/>
       <c r="V25" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W25" s="27"/>
       <c r="X25" s="27"/>
       <c r="Y25" s="27"/>
       <c r="Z25" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA25" s="27"/>
       <c r="AB25" s="27"/>
       <c r="AC25" s="27"/>
       <c r="AD25" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE25" s="27"/>
       <c r="AF25" s="27"/>
       <c r="AG25" s="27"/>
       <c r="AH25" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AI25" s="27"/>
       <c r="AJ25" s="27"/>
       <c r="AK25" s="27"/>
       <c r="AL25" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AM25" s="28"/>
       <c r="AN25" s="28"/>
@@ -2232,25 +2237,25 @@
       <c r="T26" s="26"/>
       <c r="U26" s="26"/>
       <c r="V26" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W26" s="29"/>
       <c r="X26" s="29"/>
       <c r="Y26" s="29"/>
       <c r="Z26" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA26" s="29"/>
       <c r="AB26" s="29"/>
       <c r="AC26" s="29"/>
       <c r="AD26" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AE26" s="29"/>
       <c r="AF26" s="29"/>
       <c r="AG26" s="29"/>
       <c r="AH26" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AI26" s="29"/>
       <c r="AJ26" s="29"/>
@@ -2276,7 +2281,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -3546,7 +3551,7 @@
     </row>
     <row r="51" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" s="31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
